--- a/data/heroes enemy.xlsx
+++ b/data/heroes enemy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projetos\Overwatch-Best-Picks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projetos\Overwatch-Best-Picks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA2" s="2">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>-1</v>
       </c>
       <c r="AC3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="2">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="AZ3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BA3" s="2">
         <v>-1</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="2">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="AZ5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA5" s="2">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>-1</v>
       </c>
       <c r="AZ6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA6" s="2">
         <v>-1</v>
@@ -1516,7 +1516,7 @@
         <v>-1</v>
       </c>
       <c r="AC7" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="2">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>-1</v>
       </c>
       <c r="AC8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" s="2">
         <v>0</v>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="AU8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV8" s="2">
         <v>-2</v>
@@ -1907,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="AZ9" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BA9" s="2">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="AC10" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="AZ11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA11" s="2">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="2">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="AZ15" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BA15" s="2">
         <v>1</v>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA16" s="2">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="AC17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD17" s="2">
         <v>1</v>
@@ -3448,7 +3448,7 @@
         <v>-1</v>
       </c>
       <c r="AC19" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="2">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="AZ19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA19" s="2">
         <v>1</v>
@@ -3678,7 +3678,7 @@
         <v>-1</v>
       </c>
       <c r="AZ20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BA20" s="2">
         <v>-1</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="2">
         <v>1</v>
@@ -4000,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="AZ22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA22" s="2">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD24" s="2">
         <v>-1</v>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="AZ24" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BA24" s="2">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="AZ25" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA25" s="2">
         <v>-1</v>
@@ -4575,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="AC26" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD26" s="2">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>-1</v>
       </c>
       <c r="AZ26" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA26" s="2">
         <v>0</v>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="2">
         <v>0</v>
@@ -4897,7 +4897,7 @@
         <v>-1</v>
       </c>
       <c r="AC28" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD28" s="2">
         <v>0</v>
@@ -4980,28 +4980,28 @@
         <v>-1</v>
       </c>
       <c r="C29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2">
         <v>-1</v>
       </c>
       <c r="E29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2">
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
       </c>
       <c r="J29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2">
         <v>2</v>
@@ -5013,7 +5013,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2">
         <v>1</v>
@@ -5022,13 +5022,13 @@
         <v>-1</v>
       </c>
       <c r="Q29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="2">
         <v>1</v>
       </c>
       <c r="S29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T29" s="2">
         <v>2</v>
@@ -5046,46 +5046,46 @@
         <v>1</v>
       </c>
       <c r="Y29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="2">
         <v>0</v>
       </c>
       <c r="AC29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="2">
         <v>0</v>
       </c>
       <c r="AE29" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AF29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" s="2">
         <v>0</v>
       </c>
       <c r="AI29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ29" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AK29" s="2">
         <v>0</v>
       </c>
       <c r="AL29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM29" s="2">
         <v>0</v>
@@ -5094,43 +5094,43 @@
         <v>-1</v>
       </c>
       <c r="AO29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP29" s="2">
         <v>1</v>
       </c>
       <c r="AQ29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AR29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS29" s="2">
         <v>1</v>
       </c>
       <c r="AT29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW29" s="2">
         <v>0</v>
       </c>
       <c r="AX29" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ29" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BA29" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="AM30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN30" s="2">
         <v>1</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="AZ30" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BA30" s="2">
         <v>-1</v>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD31" s="2">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" s="2">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>2</v>
       </c>
       <c r="AZ32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA32" s="2">
         <v>2</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD33" s="2">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA34" s="2">
         <v>-1</v>
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="AC35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" s="2">
         <v>-1</v>
@@ -6093,7 +6093,7 @@
         <v>-2</v>
       </c>
       <c r="AZ35" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BA35" s="2">
         <v>-1</v>
@@ -6185,7 +6185,7 @@
         <v>-1</v>
       </c>
       <c r="AC36" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AD36" s="2">
         <v>1</v>
@@ -6415,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="AZ37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA37" s="2">
         <v>0</v>
@@ -6444,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="2">
         <v>-1</v>
@@ -6576,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="AZ38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA38" s="2">
         <v>1</v>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="AD39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE39" s="2">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="AC40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD40" s="2">
         <v>1</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="AC41" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AD41" s="2">
         <v>1</v>
@@ -7059,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="AZ41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA41" s="2">
         <v>1</v>
@@ -7220,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="AZ42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA42" s="2">
         <v>2</v>
@@ -7312,7 +7312,7 @@
         <v>-1</v>
       </c>
       <c r="AC43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="2">
         <v>1</v>
@@ -7795,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="AC46" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AD46" s="2">
         <v>1</v>
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="AZ46" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BA46" s="2">
         <v>-1</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I47" s="2">
         <v>-1</v>
@@ -7956,7 +7956,7 @@
         <v>1</v>
       </c>
       <c r="AC47" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD47" s="2">
         <v>1</v>
@@ -8117,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="AC48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48" s="2">
         <v>1</v>
@@ -8278,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="AC49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD49" s="2">
         <v>2</v>
@@ -8508,7 +8508,7 @@
         <v>1</v>
       </c>
       <c r="AZ50" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BA50" s="2">
         <v>2</v>
@@ -8600,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="AC51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD51" s="2">
         <v>0</v>
@@ -8680,16 +8680,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D52" s="2">
         <v>-1</v>
       </c>
       <c r="E52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2">
         <v>-1</v>
@@ -8707,7 +8707,7 @@
         <v>-1</v>
       </c>
       <c r="K52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2">
         <v>0</v>
@@ -8716,16 +8716,16 @@
         <v>1</v>
       </c>
       <c r="N52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R52" s="2">
         <v>1</v>
@@ -8740,16 +8740,16 @@
         <v>1</v>
       </c>
       <c r="V52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W52" s="2">
         <v>0</v>
       </c>
       <c r="X52" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Y52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="2">
         <v>0</v>
@@ -8758,13 +8758,13 @@
         <v>-2</v>
       </c>
       <c r="AB52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD52" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE52" s="2">
         <v>2</v>
@@ -8773,40 +8773,40 @@
         <v>-1</v>
       </c>
       <c r="AG52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ52" s="2">
         <v>1</v>
       </c>
       <c r="AK52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM52" s="2">
         <v>2</v>
       </c>
       <c r="AN52" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ52" s="2">
         <v>-1</v>
       </c>
       <c r="AR52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS52" s="2">
         <v>-1</v>
@@ -8815,13 +8815,13 @@
         <v>1</v>
       </c>
       <c r="AU52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV52" s="2">
         <v>-1</v>
       </c>
       <c r="AW52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX52" s="2">
         <v>-2</v>
@@ -8830,10 +8830,10 @@
         <v>2</v>
       </c>
       <c r="AZ52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA52" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
@@ -8922,10 +8922,10 @@
         <v>0</v>
       </c>
       <c r="AC53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE53" s="2">
         <v>2</v>
@@ -8991,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="AZ53" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA53" s="2">
         <v>-1</v>

--- a/data/heroes enemy.xlsx
+++ b/data/heroes enemy.xlsx
@@ -636,10 +636,10 @@
         <v>-1</v>
       </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>-2</v>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2">
         <v>2</v>
@@ -675,13 +675,13 @@
         <v>-1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2">
         <v>0</v>
       </c>
       <c r="S2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" s="2">
         <v>2</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2">
         <v>-2</v>
@@ -702,31 +702,31 @@
         <v>0</v>
       </c>
       <c r="Z2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="2">
         <v>0</v>
       </c>
       <c r="AC2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="2">
         <v>1</v>
       </c>
       <c r="AG2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="2">
         <v>0</v>
@@ -744,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="AN2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="2">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
         <v>-1</v>
@@ -1113,7 +1113,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
@@ -2401,7 +2401,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -3367,7 +3367,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -3850,7 +3850,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2">
         <v>-1</v>
@@ -4494,7 +4494,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -4977,7 +4977,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -5138,7 +5138,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C33" s="2">
         <v>-1</v>
@@ -5782,7 +5782,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -6748,7 +6748,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2">
         <v>-1</v>
@@ -6909,7 +6909,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>

--- a/data/heroes enemy.xlsx
+++ b/data/heroes enemy.xlsx
@@ -1,23 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projetos\Overwatch-Best-Picks\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch-Best-Picks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9452AC1-FFD5-4EAE-BB93-9C390FD3230B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Página1 (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="53">
   <si>
     <t>Hero</t>
   </si>
@@ -181,8 +197,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -223,7 +239,13 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -243,7 +265,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -254,6 +284,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -451,20 +489,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryRight="0" summaryBelow="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="12.57031" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:BA1002"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="12.57031" customWidth="1"/>
+    <col min="1" max="7" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,7 +666,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -654,10 +695,10 @@
         <v>-2</v>
       </c>
       <c r="J2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
         <v>1</v>
@@ -711,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="2">
         <v>1</v>
@@ -726,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="AH2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" s="2">
         <v>0</v>
@@ -786,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -800,22 +841,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H3" s="2">
         <v>-2</v>
       </c>
       <c r="I3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2">
         <v>-1</v>
@@ -827,40 +868,40 @@
         <v>0</v>
       </c>
       <c r="N3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="2">
         <v>1</v>
       </c>
       <c r="Q3" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" s="2">
         <v>-1</v>
       </c>
       <c r="T3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="2">
         <v>0</v>
@@ -869,37 +910,37 @@
         <v>0</v>
       </c>
       <c r="AB3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE3" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="2">
         <v>-1</v>
       </c>
       <c r="AG3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI3" s="2">
         <v>-1</v>
       </c>
       <c r="AJ3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AK3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM3" s="2">
         <v>1</v>
@@ -908,16 +949,16 @@
         <v>1</v>
       </c>
       <c r="AO3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ3" s="2">
         <v>1</v>
       </c>
       <c r="AR3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS3" s="2">
         <v>0</v>
@@ -926,16 +967,16 @@
         <v>0</v>
       </c>
       <c r="AU3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV3" s="2">
         <v>1</v>
       </c>
       <c r="AW3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY3" s="2">
         <v>1</v>
@@ -944,10 +985,10 @@
         <v>1</v>
       </c>
       <c r="BA3" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -964,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -976,7 +1017,7 @@
         <v>-1</v>
       </c>
       <c r="J4" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2">
         <v>-1</v>
@@ -1003,7 +1044,7 @@
         <v>-1</v>
       </c>
       <c r="S4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" s="2">
         <v>1</v>
@@ -1036,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="AD4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="2">
         <v>2</v>
@@ -1048,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="AH4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" s="2">
         <v>0</v>
@@ -1078,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="AR4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS4" s="2">
         <v>-1</v>
@@ -1108,7 +1149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1116,7 +1157,7 @@
         <v>-1</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -1137,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2">
         <v>1</v>
@@ -1164,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" s="2">
         <v>0</v>
@@ -1197,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="2">
         <v>1</v>
@@ -1206,10 +1247,10 @@
         <v>1</v>
       </c>
       <c r="AG5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" s="2">
         <v>0</v>
@@ -1218,10 +1259,10 @@
         <v>1</v>
       </c>
       <c r="AK5" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="2">
         <v>1</v>
@@ -1239,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="AR5" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS5" s="2">
         <v>-1</v>
@@ -1269,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1277,10 +1318,10 @@
         <v>-1</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1289,19 +1330,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J6" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2">
         <v>1</v>
@@ -1310,7 +1351,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2">
         <v>-2</v>
@@ -1319,19 +1360,19 @@
         <v>-2</v>
       </c>
       <c r="Q6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2">
         <v>-1</v>
       </c>
       <c r="S6" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U6" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="V6" s="2">
         <v>1</v>
@@ -1346,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="2">
         <v>1</v>
@@ -1355,31 +1396,31 @@
         <v>1</v>
       </c>
       <c r="AC6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2">
         <v>1</v>
       </c>
       <c r="AE6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI6" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ6" s="2">
         <v>1</v>
       </c>
       <c r="AK6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" s="2">
         <v>-1</v>
@@ -1391,34 +1432,34 @@
         <v>-1</v>
       </c>
       <c r="AO6" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ6" s="2">
         <v>1</v>
       </c>
       <c r="AR6" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS6" s="2">
         <v>-1</v>
       </c>
       <c r="AT6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW6" s="2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" s="2">
         <v>-1</v>
@@ -1430,7 +1471,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1438,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
         <v>-1</v>
@@ -1447,7 +1488,7 @@
         <v>-1</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -1462,7 +1503,7 @@
         <v>-1</v>
       </c>
       <c r="K7" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2">
         <v>-2</v>
@@ -1486,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
@@ -1519,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="AD7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="2">
         <v>-1</v>
       </c>
       <c r="AF7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH7" s="2">
         <v>1</v>
@@ -1543,16 +1584,16 @@
         <v>0</v>
       </c>
       <c r="AL7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="2">
         <v>0</v>
       </c>
       <c r="AN7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP7" s="2">
         <v>2</v>
@@ -1588,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="BA7" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1608,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -1680,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="AD8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="2">
         <v>1</v>
@@ -1701,10 +1742,10 @@
         <v>-1</v>
       </c>
       <c r="AK8" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AL8" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM8" s="3">
         <v>0</v>
@@ -1722,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="AR8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8" s="2">
         <v>2</v>
@@ -1749,10 +1790,10 @@
         <v>-1</v>
       </c>
       <c r="BA8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1801,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -1769,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -1781,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -1793,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
@@ -1838,10 +1879,10 @@
         <v>0</v>
       </c>
       <c r="AC9" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="2">
         <v>0</v>
@@ -1850,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="AG9" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH9" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI9" s="2">
         <v>-1</v>
@@ -1862,19 +1903,19 @@
         <v>1</v>
       </c>
       <c r="AK9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL9" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="2">
         <v>1</v>
       </c>
       <c r="AN9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP9" s="2">
         <v>0</v>
@@ -1883,7 +1924,7 @@
         <v>-2</v>
       </c>
       <c r="AR9" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AS9" s="2">
         <v>0</v>
@@ -1910,27 +1951,27 @@
         <v>-1</v>
       </c>
       <c r="BA9" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F10" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -1939,22 +1980,22 @@
         <v>1</v>
       </c>
       <c r="I10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
       </c>
       <c r="K10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2">
         <v>1</v>
@@ -1969,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T10" s="2">
         <v>-1</v>
@@ -1978,28 +2019,28 @@
         <v>1</v>
       </c>
       <c r="V10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W10" s="2">
         <v>1</v>
       </c>
       <c r="X10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AA10" s="2">
         <v>-1</v>
       </c>
       <c r="AB10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" s="2">
         <v>0</v>
@@ -2008,16 +2049,16 @@
         <v>0</v>
       </c>
       <c r="AF10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AH10" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ10" s="2">
         <v>1</v>
@@ -2026,13 +2067,13 @@
         <v>0</v>
       </c>
       <c r="AL10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM10" s="2">
         <v>-1</v>
       </c>
       <c r="AN10" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AO10" s="2">
         <v>0</v>
@@ -2044,57 +2085,57 @@
         <v>-1</v>
       </c>
       <c r="AR10" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AS10" s="2">
         <v>0</v>
       </c>
       <c r="AT10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AU10" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV10" s="2">
         <v>1</v>
       </c>
       <c r="AW10" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX10" s="2">
         <v>1</v>
       </c>
       <c r="AY10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ10" s="2">
         <v>1</v>
       </c>
       <c r="BA10" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F11" s="2">
         <v>-1</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2">
         <v>-2</v>
@@ -2103,10 +2144,10 @@
         <v>-1</v>
       </c>
       <c r="J11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2">
         <v>-1</v>
@@ -2115,16 +2156,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2">
         <v>0</v>
       </c>
       <c r="P11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="2">
         <v>0</v>
@@ -2133,7 +2174,7 @@
         <v>-1</v>
       </c>
       <c r="T11" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U11" s="2">
         <v>0</v>
@@ -2145,28 +2186,28 @@
         <v>1</v>
       </c>
       <c r="X11" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="2">
         <v>1</v>
       </c>
       <c r="Z11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AA11" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" s="2">
         <v>-2</v>
       </c>
       <c r="AD11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AF11" s="2">
         <v>-1</v>
@@ -2175,34 +2216,34 @@
         <v>-1</v>
       </c>
       <c r="AH11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="2">
         <v>-2</v>
       </c>
       <c r="AK11" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AL11" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP11" s="2">
         <v>-2</v>
       </c>
       <c r="AQ11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR11" s="2">
         <v>-1</v>
@@ -2211,31 +2252,31 @@
         <v>0</v>
       </c>
       <c r="AT11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW11" s="2">
         <v>1</v>
       </c>
       <c r="AX11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY11" s="2">
         <v>1</v>
       </c>
       <c r="AZ11" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2324,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="AD12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="2">
         <v>1</v>
@@ -2336,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="AH12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" s="2">
         <v>1</v>
@@ -2345,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="AK12" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL12" s="2">
         <v>-1</v>
@@ -2396,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -2425,7 +2466,7 @@
         <v>-1</v>
       </c>
       <c r="J13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -2482,7 +2523,7 @@
         <v>-1</v>
       </c>
       <c r="AC13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="2">
         <v>1</v>
@@ -2497,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="AH13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" s="2">
         <v>0</v>
@@ -2509,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="AL13" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM13" s="2">
         <v>0</v>
@@ -2554,10 +2595,10 @@
         <v>-1</v>
       </c>
       <c r="BA13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2652,13 +2693,13 @@
         <v>1</v>
       </c>
       <c r="AF14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="2">
         <v>-1</v>
@@ -2667,10 +2708,10 @@
         <v>1</v>
       </c>
       <c r="AK14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" s="2">
         <v>1</v>
@@ -2679,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="AO14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP14" s="2">
         <v>0</v>
@@ -2688,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="AR14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS14" s="2">
         <v>-1</v>
@@ -2715,10 +2756,10 @@
         <v>1</v>
       </c>
       <c r="BA14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2726,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -2807,7 +2848,7 @@
         <v>-1</v>
       </c>
       <c r="AD15" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AE15" s="2">
         <v>0</v>
@@ -2831,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="AL15" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM15" s="2">
         <v>0</v>
@@ -2849,7 +2890,7 @@
         <v>-1</v>
       </c>
       <c r="AR15" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS15" s="2">
         <v>0</v>
@@ -2879,7 +2920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2911,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="2">
         <v>-1</v>
@@ -2944,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="W16" s="2">
         <v>0</v>
@@ -2968,19 +3009,19 @@
         <v>1</v>
       </c>
       <c r="AD16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="2">
         <v>1</v>
       </c>
       <c r="AF16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG16" s="2">
         <v>1</v>
       </c>
       <c r="AH16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="2">
         <v>1</v>
@@ -2989,10 +3030,10 @@
         <v>1</v>
       </c>
       <c r="AK16" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM16" s="2">
         <v>0</v>
@@ -3010,10 +3051,10 @@
         <v>1</v>
       </c>
       <c r="AR16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS16" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AT16" s="2">
         <v>-1</v>
@@ -3040,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -3072,7 +3113,7 @@
         <v>-1</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2">
         <v>-1</v>
@@ -3096,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T17" s="2">
         <v>1</v>
@@ -3138,10 +3179,10 @@
         <v>-1</v>
       </c>
       <c r="AG17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AH17" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AI17" s="2">
         <v>0</v>
@@ -3150,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="AK17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" s="2">
         <v>1</v>
@@ -3162,7 +3203,7 @@
         <v>-1</v>
       </c>
       <c r="AO17" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP17" s="2">
         <v>-1</v>
@@ -3198,10 +3239,10 @@
         <v>0</v>
       </c>
       <c r="BA17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -3209,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -3287,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="AC18" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="2">
         <v>1</v>
@@ -3302,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="AH18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" s="2">
         <v>-1</v>
@@ -3314,7 +3355,7 @@
         <v>-1</v>
       </c>
       <c r="AL18" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM18" s="2">
         <v>0</v>
@@ -3362,7 +3403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -3373,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E19" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2">
         <v>-2</v>
@@ -3391,10 +3432,10 @@
         <v>-1</v>
       </c>
       <c r="J19" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2">
         <v>2</v>
@@ -3427,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="V19" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" s="2">
         <v>1</v>
@@ -3436,13 +3477,13 @@
         <v>0</v>
       </c>
       <c r="Y19" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="2">
         <v>0</v>
       </c>
       <c r="AA19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB19" s="2">
         <v>-1</v>
@@ -3457,16 +3498,16 @@
         <v>0</v>
       </c>
       <c r="AF19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG19" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH19" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AI19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" s="2">
         <v>1</v>
@@ -3475,16 +3516,16 @@
         <v>0</v>
       </c>
       <c r="AL19" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AM19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AP19" s="2">
         <v>0</v>
@@ -3493,19 +3534,19 @@
         <v>1</v>
       </c>
       <c r="AR19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS19" s="2">
         <v>1</v>
       </c>
       <c r="AT19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" s="2">
         <v>0</v>
       </c>
       <c r="AV19" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AW19" s="2">
         <v>0</v>
@@ -3517,13 +3558,13 @@
         <v>1</v>
       </c>
       <c r="AZ19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA19" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3540,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -3555,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
@@ -3609,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="AC20" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD20" s="2">
         <v>-1</v>
@@ -3618,7 +3659,7 @@
         <v>2</v>
       </c>
       <c r="AF20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG20" s="2">
         <v>0</v>
@@ -3636,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="AL20" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM20" s="2">
         <v>-1</v>
@@ -3645,7 +3686,7 @@
         <v>-1</v>
       </c>
       <c r="AO20" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AP20" s="2">
         <v>1</v>
@@ -3681,10 +3722,10 @@
         <v>-2</v>
       </c>
       <c r="BA20" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -3692,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
         <v>-1</v>
@@ -3740,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T21" s="2">
         <v>1</v>
@@ -3770,7 +3811,7 @@
         <v>-2</v>
       </c>
       <c r="AC21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21" s="2">
         <v>1</v>
@@ -3779,10 +3820,10 @@
         <v>-1</v>
       </c>
       <c r="AF21" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AG21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="2">
         <v>1</v>
@@ -3794,10 +3835,10 @@
         <v>0</v>
       </c>
       <c r="AK21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" s="2">
         <v>0</v>
@@ -3815,7 +3856,7 @@
         <v>2</v>
       </c>
       <c r="AR21" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS21" s="2">
         <v>0</v>
@@ -3842,10 +3883,10 @@
         <v>-1</v>
       </c>
       <c r="BA21" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -3853,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -3862,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -3874,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
@@ -3892,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="2">
         <v>-2</v>
@@ -3901,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="S22" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T22" s="2">
         <v>1</v>
@@ -3934,19 +3975,19 @@
         <v>0</v>
       </c>
       <c r="AD22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="2">
         <v>0</v>
       </c>
       <c r="AF22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI22" s="2">
         <v>1</v>
@@ -3955,19 +3996,19 @@
         <v>1</v>
       </c>
       <c r="AK22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL22" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM22" s="2">
         <v>1</v>
       </c>
       <c r="AN22" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO22" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP22" s="2">
         <v>-1</v>
@@ -3976,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="AR22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS22" s="2">
         <v>-1</v>
@@ -4003,10 +4044,10 @@
         <v>1</v>
       </c>
       <c r="BA22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -4014,7 +4055,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -4116,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="AK23" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL23" s="2">
         <v>1</v>
@@ -4167,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -4175,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2">
         <v>-1</v>
@@ -4184,7 +4225,7 @@
         <v>-1</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -4196,10 +4237,10 @@
         <v>-1</v>
       </c>
       <c r="J24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="2">
         <v>-1</v>
@@ -4223,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" s="2">
         <v>0</v>
@@ -4253,10 +4294,10 @@
         <v>0</v>
       </c>
       <c r="AC24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="2">
         <v>-1</v>
@@ -4265,10 +4306,10 @@
         <v>-1</v>
       </c>
       <c r="AG24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="2">
         <v>1</v>
@@ -4277,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="AK24" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL24" s="2">
         <v>0</v>
@@ -4289,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AP24" s="2">
         <v>-1</v>
@@ -4298,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="AR24" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS24" s="2">
         <v>-1</v>
@@ -4328,7 +4369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -4336,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -4345,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -4357,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2">
         <v>-1</v>
@@ -4384,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="2">
         <v>0</v>
@@ -4417,13 +4458,13 @@
         <v>0</v>
       </c>
       <c r="AD25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="2">
         <v>0</v>
       </c>
       <c r="AF25" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG25" s="2">
         <v>0</v>
@@ -4438,10 +4479,10 @@
         <v>1</v>
       </c>
       <c r="AK25" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AL25" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM25" s="2">
         <v>0</v>
@@ -4450,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25" s="2">
         <v>-1</v>
@@ -4459,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="AR25" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS25" s="2">
         <v>1</v>
@@ -4486,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="BA25" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -4506,7 +4547,7 @@
         <v>-1</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -4518,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K26" s="2">
         <v>1</v>
@@ -4587,10 +4628,10 @@
         <v>-1</v>
       </c>
       <c r="AG26" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI26" s="2">
         <v>0</v>
@@ -4608,10 +4649,10 @@
         <v>-2</v>
       </c>
       <c r="AN26" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26" s="2">
         <v>1</v>
@@ -4620,7 +4661,7 @@
         <v>-1</v>
       </c>
       <c r="AR26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS26" s="2">
         <v>0</v>
@@ -4647,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="BA26" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -4682,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2">
         <v>0</v>
@@ -4706,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T27" s="2">
         <v>1</v>
@@ -4745,10 +4786,10 @@
         <v>-1</v>
       </c>
       <c r="AF27" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH27" s="2">
         <v>1</v>
@@ -4811,7 +4852,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -4819,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -4828,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -4840,10 +4881,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="2">
         <v>1</v>
@@ -4909,10 +4950,10 @@
         <v>1</v>
       </c>
       <c r="AG28" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" s="2">
         <v>0</v>
@@ -4921,10 +4962,10 @@
         <v>1</v>
       </c>
       <c r="AK28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="2">
         <v>0</v>
@@ -4933,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="AO28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28" s="2">
         <v>-1</v>
@@ -4942,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="AR28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS28" s="2">
         <v>0</v>
@@ -4969,18 +5010,18 @@
         <v>-1</v>
       </c>
       <c r="BA28" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2">
         <v>-1</v>
@@ -4989,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -4998,10 +5039,10 @@
         <v>-1</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K29" s="2">
         <v>2</v>
@@ -5010,7 +5051,7 @@
         <v>-1</v>
       </c>
       <c r="M29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2">
         <v>0</v>
@@ -5025,16 +5066,16 @@
         <v>1</v>
       </c>
       <c r="R29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="2">
         <v>0</v>
       </c>
       <c r="T29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V29" s="2">
         <v>0</v>
@@ -5043,7 +5084,7 @@
         <v>-1</v>
       </c>
       <c r="X29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="2">
         <v>0</v>
@@ -5073,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="AH29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" s="2">
         <v>-1</v>
@@ -5088,16 +5129,16 @@
         <v>-1</v>
       </c>
       <c r="AM29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN29" s="2">
         <v>-1</v>
       </c>
       <c r="AO29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ29" s="2">
         <v>0</v>
@@ -5118,7 +5159,7 @@
         <v>-1</v>
       </c>
       <c r="AW29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX29" s="2">
         <v>2</v>
@@ -5130,10 +5171,10 @@
         <v>-1</v>
       </c>
       <c r="BA29" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -5141,58 +5182,58 @@
         <v>-1</v>
       </c>
       <c r="C30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2">
         <v>-1</v>
       </c>
       <c r="N30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q30" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R30" s="2">
         <v>-1</v>
       </c>
       <c r="S30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" s="2">
         <v>-1</v>
@@ -5204,10 +5245,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="2">
         <v>0</v>
@@ -5222,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AD30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="2">
         <v>0</v>
@@ -5234,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="AH30" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI30" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AJ30" s="2">
         <v>-1</v>
@@ -5246,43 +5287,43 @@
         <v>0</v>
       </c>
       <c r="AL30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ30" s="2">
         <v>-1</v>
       </c>
       <c r="AR30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AS30" s="2">
         <v>-1</v>
       </c>
       <c r="AT30" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AU30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV30" s="2">
         <v>-1</v>
       </c>
       <c r="AW30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX30" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY30" s="2">
         <v>0</v>
@@ -5291,10 +5332,10 @@
         <v>1</v>
       </c>
       <c r="BA30" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -5302,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
         <v>-2</v>
@@ -5311,7 +5352,7 @@
         <v>-1</v>
       </c>
       <c r="F31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -5326,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2">
         <v>-1</v>
@@ -5389,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="AF31" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG31" s="2">
         <v>0</v>
@@ -5407,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="AL31" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="2">
         <v>0</v>
@@ -5455,7 +5496,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -5463,7 +5504,7 @@
         <v>-1</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2">
         <v>-2</v>
@@ -5472,7 +5513,7 @@
         <v>-1</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -5484,7 +5525,7 @@
         <v>-1</v>
       </c>
       <c r="J32" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
@@ -5496,25 +5537,25 @@
         <v>-2</v>
       </c>
       <c r="N32" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2">
         <v>1</v>
       </c>
       <c r="P32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="2">
         <v>-2</v>
       </c>
       <c r="S32" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T32" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U32" s="2">
         <v>2</v>
@@ -5529,16 +5570,16 @@
         <v>1</v>
       </c>
       <c r="Y32" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="2">
         <v>1</v>
       </c>
       <c r="AA32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC32" s="2">
         <v>1</v>
@@ -5547,19 +5588,19 @@
         <v>1</v>
       </c>
       <c r="AE32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF32" s="2">
         <v>0</v>
       </c>
       <c r="AG32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" s="2">
         <v>1</v>
@@ -5574,19 +5615,19 @@
         <v>1</v>
       </c>
       <c r="AN32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AP32" s="2">
         <v>0</v>
       </c>
       <c r="AQ32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS32" s="2">
         <v>1</v>
@@ -5598,25 +5639,25 @@
         <v>1</v>
       </c>
       <c r="AV32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW32" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX32" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AY32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ32" s="2">
         <v>1</v>
       </c>
       <c r="BA32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -5624,31 +5665,31 @@
         <v>-1</v>
       </c>
       <c r="C33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="2">
         <v>-1</v>
       </c>
       <c r="E33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="2">
         <v>-1</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2">
         <v>-1</v>
@@ -5657,7 +5698,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O33" s="2">
         <v>0</v>
@@ -5666,37 +5707,37 @@
         <v>-1</v>
       </c>
       <c r="Q33" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R33" s="2">
         <v>-1</v>
       </c>
       <c r="S33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W33" s="2">
         <v>-1</v>
       </c>
       <c r="X33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA33" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AB33" s="2">
         <v>0</v>
@@ -5711,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="AF33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG33" s="2">
         <v>0</v>
@@ -5735,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="AN33" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO33" s="2">
         <v>0</v>
@@ -5753,51 +5794,51 @@
         <v>0</v>
       </c>
       <c r="AT33" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY33" s="2">
         <v>-1</v>
       </c>
       <c r="AZ33" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA33" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="2">
         <v>-1</v>
@@ -5806,40 +5847,40 @@
         <v>1</v>
       </c>
       <c r="J34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2">
         <v>0</v>
       </c>
       <c r="P34" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q34" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S34" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="T34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V34" s="2">
         <v>-1</v>
@@ -5848,97 +5889,97 @@
         <v>-1</v>
       </c>
       <c r="X34" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="2">
         <v>0</v>
       </c>
       <c r="Z34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="2">
         <v>-1</v>
       </c>
       <c r="AB34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" s="2">
         <v>0</v>
       </c>
       <c r="AF34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="2">
         <v>1</v>
       </c>
       <c r="AK34" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AL34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM34" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AN34" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AO34" s="2">
         <v>0</v>
       </c>
       <c r="AP34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ34" s="2">
         <v>-1</v>
       </c>
       <c r="AR34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS34" s="2">
         <v>-1</v>
       </c>
       <c r="AT34" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV34" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AW34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX34" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AY34" s="2">
         <v>0</v>
       </c>
       <c r="AZ34" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA34" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -5946,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -5955,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
@@ -5967,10 +6008,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2">
         <v>-1</v>
@@ -5994,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="S35" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="T35" s="2">
         <v>2</v>
@@ -6027,19 +6068,19 @@
         <v>1</v>
       </c>
       <c r="AD35" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE35" s="2">
         <v>-1</v>
       </c>
       <c r="AF35" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG35" s="2">
         <v>-1</v>
       </c>
       <c r="AH35" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI35" s="2">
         <v>0</v>
@@ -6048,10 +6089,10 @@
         <v>1</v>
       </c>
       <c r="AK35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM35" s="2">
         <v>1</v>
@@ -6060,7 +6101,7 @@
         <v>-1</v>
       </c>
       <c r="AO35" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP35" s="2">
         <v>0</v>
@@ -6099,7 +6140,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -6107,7 +6148,7 @@
         <v>-2</v>
       </c>
       <c r="C36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -6209,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="AK36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM36" s="2">
         <v>-1</v>
@@ -6260,7 +6301,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -6268,49 +6309,49 @@
         <v>1</v>
       </c>
       <c r="C37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I37" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
       </c>
       <c r="K37" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
       </c>
       <c r="N37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R37" s="2">
         <v>1</v>
@@ -6322,19 +6363,19 @@
         <v>0</v>
       </c>
       <c r="U37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="2">
         <v>0</v>
@@ -6343,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="AB37" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AC37" s="2">
         <v>0</v>
@@ -6361,16 +6402,16 @@
         <v>0</v>
       </c>
       <c r="AH37" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AI37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AK37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" s="2">
         <v>0</v>
@@ -6379,31 +6420,31 @@
         <v>0</v>
       </c>
       <c r="AN37" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AO37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP37" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ37" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR37" s="2">
         <v>0</v>
       </c>
       <c r="AS37" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AT37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV37" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW37" s="2">
         <v>0</v>
@@ -6412,16 +6453,16 @@
         <v>0</v>
       </c>
       <c r="AY37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ37" s="2">
         <v>-1</v>
       </c>
       <c r="BA37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -6435,85 +6476,85 @@
         <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
         <v>1</v>
       </c>
       <c r="M38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2">
         <v>-1</v>
       </c>
       <c r="O38" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="2">
         <v>0</v>
       </c>
       <c r="V38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" s="2">
         <v>-1</v>
       </c>
       <c r="X38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z38" s="2">
         <v>1</v>
       </c>
       <c r="AA38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC38" s="2">
         <v>1</v>
       </c>
       <c r="AD38" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF38" s="2">
         <v>0</v>
@@ -6528,25 +6569,25 @@
         <v>0</v>
       </c>
       <c r="AJ38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" s="2">
         <v>0</v>
       </c>
       <c r="AM38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ38" s="2">
         <v>1</v>
@@ -6558,31 +6599,31 @@
         <v>0</v>
       </c>
       <c r="AT38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AW38" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AX38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY38" s="2">
         <v>0</v>
       </c>
       <c r="AZ38" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -6614,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2">
         <v>-1</v>
@@ -6638,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T39" s="2">
         <v>1</v>
@@ -6668,10 +6709,10 @@
         <v>0</v>
       </c>
       <c r="AC39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE39" s="2">
         <v>0</v>
@@ -6683,7 +6724,7 @@
         <v>-1</v>
       </c>
       <c r="AH39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI39" s="2">
         <v>-1</v>
@@ -6695,7 +6736,7 @@
         <v>0</v>
       </c>
       <c r="AL39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM39" s="2">
         <v>0</v>
@@ -6740,10 +6781,10 @@
         <v>-2</v>
       </c>
       <c r="BA39" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -6760,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -6775,7 +6816,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="2">
         <v>0</v>
@@ -6799,16 +6840,16 @@
         <v>0</v>
       </c>
       <c r="S40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" s="2">
         <v>1</v>
       </c>
       <c r="V40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="2">
         <v>0</v>
@@ -6817,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="Y40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="2">
         <v>2</v>
@@ -6826,25 +6867,25 @@
         <v>0</v>
       </c>
       <c r="AB40" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC40" s="2">
         <v>1</v>
       </c>
       <c r="AD40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE40" s="2">
         <v>1</v>
       </c>
       <c r="AF40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG40" s="2">
         <v>1</v>
       </c>
       <c r="AH40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI40" s="2">
         <v>1</v>
@@ -6853,7 +6894,7 @@
         <v>2</v>
       </c>
       <c r="AK40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" s="2">
         <v>0</v>
@@ -6880,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="AT40" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AU40" s="2">
         <v>0</v>
@@ -6904,7 +6945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -6912,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D41" s="2">
         <v>-1</v>
@@ -6921,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -6933,7 +6974,7 @@
         <v>-2</v>
       </c>
       <c r="J41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="2">
         <v>-2</v>
@@ -6960,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" s="2">
         <v>0</v>
@@ -6990,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="AC41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD41" s="2">
         <v>1</v>
@@ -6999,13 +7040,13 @@
         <v>0</v>
       </c>
       <c r="AF41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG41" s="2">
         <v>0</v>
       </c>
       <c r="AH41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="2">
         <v>1</v>
@@ -7014,10 +7055,10 @@
         <v>0</v>
       </c>
       <c r="AK41" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM41" s="2">
         <v>-1</v>
@@ -7035,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="AR41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="2">
         <v>1</v>
@@ -7065,7 +7106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -7073,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -7082,7 +7123,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2">
         <v>-2</v>
@@ -7151,10 +7192,10 @@
         <v>1</v>
       </c>
       <c r="AC42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="2">
         <v>-1</v>
@@ -7166,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="AH42" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="2">
         <v>0</v>
@@ -7175,10 +7216,10 @@
         <v>1</v>
       </c>
       <c r="AK42" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AL42" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM42" s="2">
         <v>2</v>
@@ -7226,7 +7267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -7258,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="2">
         <v>-2</v>
@@ -7321,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="AF43" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG43" s="2">
         <v>1</v>
@@ -7336,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="AK43" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL43" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM43" s="2">
         <v>2</v>
@@ -7387,7 +7428,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -7395,31 +7436,31 @@
         <v>0</v>
       </c>
       <c r="C44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
       </c>
       <c r="K44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
         <v>-1</v>
@@ -7428,40 +7469,40 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="2">
         <v>-1</v>
       </c>
       <c r="S44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T44" s="2">
         <v>0</v>
       </c>
       <c r="U44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W44" s="2">
         <v>-1</v>
       </c>
       <c r="X44" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Z44" s="2">
         <v>1</v>
@@ -7470,28 +7511,28 @@
         <v>0</v>
       </c>
       <c r="AB44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC44" s="2">
         <v>0</v>
       </c>
       <c r="AD44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE44" s="2">
         <v>0</v>
       </c>
       <c r="AF44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AG44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI44" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ44" s="2">
         <v>-1</v>
@@ -7506,10 +7547,10 @@
         <v>-1</v>
       </c>
       <c r="AN44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP44" s="2">
         <v>1</v>
@@ -7521,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="AS44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT44" s="2">
         <v>1</v>
@@ -7530,25 +7571,25 @@
         <v>0</v>
       </c>
       <c r="AV44" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW44" s="2">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AX44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY44" s="2">
         <v>-1</v>
       </c>
       <c r="AZ44" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA44" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
@@ -7595,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="2">
         <v>0</v>
@@ -7661,7 +7702,7 @@
         <v>-1</v>
       </c>
       <c r="AL45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM45" s="2">
         <v>0</v>
@@ -7679,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="AR45" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS45" s="2">
         <v>0</v>
@@ -7709,7 +7750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -7717,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
@@ -7738,10 +7779,10 @@
         <v>2</v>
       </c>
       <c r="J46" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L46" s="2">
         <v>-2</v>
@@ -7798,7 +7839,7 @@
         <v>-2</v>
       </c>
       <c r="AD46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="2">
         <v>-2</v>
@@ -7807,7 +7848,7 @@
         <v>-1</v>
       </c>
       <c r="AG46" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH46" s="2">
         <v>-1</v>
@@ -7819,10 +7860,10 @@
         <v>-2</v>
       </c>
       <c r="AK46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" s="2">
         <v>-1</v>
@@ -7831,7 +7872,7 @@
         <v>-1</v>
       </c>
       <c r="AO46" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP46" s="2">
         <v>-1</v>
@@ -7867,10 +7908,10 @@
         <v>-1</v>
       </c>
       <c r="BA46" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -7878,7 +7919,7 @@
         <v>2</v>
       </c>
       <c r="C47" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -7902,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="2">
         <v>-1</v>
@@ -7926,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="S47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" s="2">
         <v>0</v>
@@ -7959,7 +8000,7 @@
         <v>-2</v>
       </c>
       <c r="AD47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE47" s="2">
         <v>0</v>
@@ -7968,7 +8009,7 @@
         <v>-1</v>
       </c>
       <c r="AG47" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH47" s="2">
         <v>-1</v>
@@ -7980,7 +8021,7 @@
         <v>-1</v>
       </c>
       <c r="AK47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL47" s="2">
         <v>0</v>
@@ -7992,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="AO47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP47" s="2">
         <v>-1</v>
@@ -8001,7 +8042,7 @@
         <v>2</v>
       </c>
       <c r="AR47" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS47" s="2">
         <v>1</v>
@@ -8028,10 +8069,10 @@
         <v>-1</v>
       </c>
       <c r="BA47" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
@@ -8039,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
@@ -8048,7 +8089,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
@@ -8060,10 +8101,10 @@
         <v>1</v>
       </c>
       <c r="J48" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K48" s="2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="2">
         <v>1</v>
@@ -8087,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="S48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="2">
         <v>0</v>
@@ -8129,10 +8170,10 @@
         <v>1</v>
       </c>
       <c r="AG48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI48" s="2">
         <v>-1</v>
@@ -8141,10 +8182,10 @@
         <v>0</v>
       </c>
       <c r="AK48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM48" s="2">
         <v>-1</v>
@@ -8162,7 +8203,7 @@
         <v>1</v>
       </c>
       <c r="AR48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS48" s="2">
         <v>0</v>
@@ -8189,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="BA48" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
@@ -8200,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="C49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2">
         <v>1</v>
@@ -8221,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K49" s="2">
         <v>-1</v>
@@ -8278,19 +8319,19 @@
         <v>1</v>
       </c>
       <c r="AC49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE49" s="2">
         <v>-1</v>
       </c>
       <c r="AF49" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH49" s="2">
         <v>-2</v>
@@ -8305,13 +8346,13 @@
         <v>0</v>
       </c>
       <c r="AL49" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AM49" s="2">
         <v>0</v>
       </c>
       <c r="AN49" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO49" s="2">
         <v>1</v>
@@ -8323,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="AR49" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS49" s="2">
         <v>0</v>
@@ -8350,10 +8391,10 @@
         <v>0</v>
       </c>
       <c r="BA49" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
@@ -8361,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
@@ -8370,7 +8411,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
@@ -8382,7 +8423,7 @@
         <v>-1</v>
       </c>
       <c r="J50" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K50" s="2">
         <v>0</v>
@@ -8409,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="S50" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T50" s="2">
         <v>-2</v>
@@ -8448,13 +8489,13 @@
         <v>-1</v>
       </c>
       <c r="AF50" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AH50" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI50" s="2">
         <v>0</v>
@@ -8466,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="AL50" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM50" s="2">
         <v>0</v>
@@ -8484,7 +8525,7 @@
         <v>2</v>
       </c>
       <c r="AR50" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AS50" s="2">
         <v>-1</v>
@@ -8514,7 +8555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -8543,7 +8584,7 @@
         <v>-1</v>
       </c>
       <c r="J51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="2">
         <v>-1</v>
@@ -8609,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="AF51" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG51" s="2">
         <v>1</v>
@@ -8624,7 +8665,7 @@
         <v>2</v>
       </c>
       <c r="AK51" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL51" s="2">
         <v>0</v>
@@ -8675,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -8707,7 +8748,7 @@
         <v>-1</v>
       </c>
       <c r="K52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2">
         <v>0</v>
@@ -8731,7 +8772,7 @@
         <v>1</v>
       </c>
       <c r="S52" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T52" s="2">
         <v>2</v>
@@ -8773,10 +8814,10 @@
         <v>-1</v>
       </c>
       <c r="AG52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" s="2">
         <v>-1</v>
@@ -8788,7 +8829,7 @@
         <v>1</v>
       </c>
       <c r="AL52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM52" s="2">
         <v>2</v>
@@ -8806,7 +8847,7 @@
         <v>-1</v>
       </c>
       <c r="AR52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS52" s="2">
         <v>-1</v>
@@ -8836,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
@@ -8856,25 +8897,25 @@
         <v>1</v>
       </c>
       <c r="G53" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I53" s="2">
         <v>-2</v>
       </c>
       <c r="J53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2">
         <v>-1</v>
       </c>
       <c r="M53" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2">
         <v>-2</v>
@@ -8886,19 +8927,19 @@
         <v>-1</v>
       </c>
       <c r="Q53" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R53" s="2">
         <v>0</v>
       </c>
       <c r="S53" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T53" s="2">
         <v>2</v>
       </c>
       <c r="U53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="2">
         <v>-1</v>
@@ -8907,37 +8948,37 @@
         <v>0</v>
       </c>
       <c r="X53" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y53" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA53" s="2">
         <v>1</v>
       </c>
       <c r="AB53" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE53" s="2">
         <v>2</v>
       </c>
       <c r="AF53" s="2">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI53" s="2">
         <v>1</v>
@@ -8946,19 +8987,19 @@
         <v>2</v>
       </c>
       <c r="AK53" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AL53" s="2">
         <v>0</v>
       </c>
       <c r="AM53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN53" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO53" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AP53" s="2">
         <v>-2</v>
@@ -8967,25 +9008,25 @@
         <v>1</v>
       </c>
       <c r="AR53" s="2">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AS53" s="2">
         <v>-2</v>
       </c>
       <c r="AT53" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AU53" s="2">
         <v>-2</v>
       </c>
       <c r="AV53" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AW53" s="2">
         <v>1</v>
       </c>
       <c r="AX53" s="2">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY53" s="2">
         <v>0</v>
@@ -8994,972 +9035,972 @@
         <v>0</v>
       </c>
       <c r="BA53" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J54" s="2"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="55" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <conditionalFormatting sqref="B2:BA53">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>B2&lt;&gt;-INDIRECT(ADDRESS(MATCH(B$1,$A:$A,0),MATCH($A2,$1:$1,0)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J54">
-    <cfRule priority="1" dxfId="0" type="expression">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>J54&lt;&gt;-INDIRECT(ADDRESS(MATCH(J$1,$A:$A,0),MATCH($A54,$1:$1,0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BA53">
-    <cfRule priority="2" dxfId="0" type="expression">
-      <formula>B2&lt;&gt;-INDIRECT(ADDRESS(MATCH(B$1,$A:$A,0),MATCH($A2,$1:$1,0)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.5118055" right="0.5118055" top="0.7875" bottom="0.7875" header="0" footer="0"/>
+  <pageMargins left="0.51180550000000002" right="0.51180550000000002" top="0.78749999999999998" bottom="0.78749999999999998" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/data/heroes enemy.xlsx
+++ b/data/heroes enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAVI\Projeto\Overwatch-Best-Picks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9452AC1-FFD5-4EAE-BB93-9C390FD3230B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664F36BA-EFA3-4EDA-99C9-550F072F9F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1682,7 +1682,7 @@
         <v>-1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R8" s="2">
         <v>-1</v>
